--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU10/HRM/post DFS_HRM-2031-0220/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU10_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.00995</v>
+        <v>17.95488</v>
       </c>
       <c r="D2" t="n">
-        <v>17.20965</v>
+        <v>17.34083</v>
       </c>
       <c r="E2" t="n">
-        <v>17.71703</v>
+        <v>17.86324</v>
       </c>
       <c r="F2" t="n">
-        <v>45.21378</v>
+        <v>45.51702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05316</v>
+        <v>0.05228</v>
       </c>
       <c r="H2" t="n">
-        <v>1.90945</v>
+        <v>1.92764</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.70819</v>
+        <v>17.86528</v>
       </c>
       <c r="D3" t="n">
-        <v>17.52001</v>
+        <v>17.44276</v>
       </c>
       <c r="E3" t="n">
-        <v>17.32573</v>
+        <v>17.56736</v>
       </c>
       <c r="F3" t="n">
-        <v>44.17604</v>
+        <v>44.11034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05283</v>
+        <v>0.05406</v>
       </c>
       <c r="H3" t="n">
-        <v>1.94899</v>
+        <v>1.88465</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.47864</v>
+        <v>17.48442</v>
       </c>
       <c r="D4" t="n">
-        <v>17.14179</v>
+        <v>16.95188</v>
       </c>
       <c r="E4" t="n">
-        <v>17.36194</v>
+        <v>17.15597</v>
       </c>
       <c r="F4" t="n">
-        <v>44.71134</v>
+        <v>44.8735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05269</v>
+        <v>0.05214</v>
       </c>
       <c r="H4" t="n">
-        <v>1.91105</v>
+        <v>1.87098</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.44364</v>
+        <v>17.36349</v>
       </c>
       <c r="D6" t="n">
-        <v>17.03327</v>
+        <v>16.84053</v>
       </c>
       <c r="E6" t="n">
-        <v>16.82119</v>
+        <v>17.18562</v>
       </c>
       <c r="F6" t="n">
-        <v>23.09702</v>
+        <v>23.34913</v>
       </c>
       <c r="G6" t="n">
-        <v>36.24319</v>
+        <v>35.53544</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.35157</v>
+        <v>17.32606</v>
       </c>
       <c r="D7" t="n">
-        <v>16.60233</v>
+        <v>16.27623</v>
       </c>
       <c r="E7" t="n">
-        <v>16.88067</v>
+        <v>17.10376</v>
       </c>
       <c r="F7" t="n">
-        <v>22.47775</v>
+        <v>22.73813</v>
       </c>
       <c r="G7" t="n">
-        <v>36.03718</v>
+        <v>35.84878</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.17439</v>
+        <v>17.46955</v>
       </c>
       <c r="D8" t="n">
-        <v>16.72877</v>
+        <v>16.8825</v>
       </c>
       <c r="E8" t="n">
-        <v>17.18011</v>
+        <v>17.06143</v>
       </c>
       <c r="F8" t="n">
-        <v>22.6045</v>
+        <v>22.82559</v>
       </c>
       <c r="G8" t="n">
-        <v>35.16253</v>
+        <v>35.96896</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.6177</v>
+        <v>0.63223</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14689</v>
+        <v>1.16579</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.63652</v>
+        <v>0.64085</v>
       </c>
       <c r="D11" t="n">
-        <v>1.15654</v>
+        <v>1.17981</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.63814</v>
+        <v>0.62402</v>
       </c>
       <c r="D12" t="n">
-        <v>1.17341</v>
+        <v>1.19135</v>
       </c>
     </row>
   </sheetData>
